--- a/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición</t>
+          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +677,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>123,81; 135,6</t>
+          <t>123,51; 135,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123,08; 134,27</t>
+          <t>122,85; 134,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121,08; 136,37</t>
+          <t>121,52; 136,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122,68; 134,16</t>
+          <t>123,05; 134,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>126,08; 138,93</t>
+          <t>126,44; 138,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>125,72; 141,14</t>
+          <t>125,53; 142,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>124,47; 133,06</t>
+          <t>125,0; 133,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>126,43; 135,06</t>
+          <t>126,55; 135,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126,18; 136,72</t>
+          <t>125,9; 136,93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>123,79; 133,09</t>
+          <t>122,8; 132,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127,41; 136,33</t>
+          <t>127,44; 136,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,68; 157,04</t>
+          <t>132,89; 157,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124,16; 132,29</t>
+          <t>124,04; 132,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>125,74; 134,11</t>
+          <t>125,66; 134,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>131,5; 149,73</t>
+          <t>130,51; 149,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>125,09; 131,46</t>
+          <t>125,13; 131,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>127,82; 134,2</t>
+          <t>128,25; 133,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>134,8; 153,26</t>
+          <t>134,77; 153,59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>121,0; 131,04</t>
+          <t>121,03; 131,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127,77; 138,56</t>
+          <t>127,57; 138,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134,0; 147,33</t>
+          <t>133,52; 147,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129,27; 140,76</t>
+          <t>128,94; 140,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125,67; 136,18</t>
+          <t>126,28; 136,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>129,0; 145,46</t>
+          <t>129,1; 144,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126,8; 134,75</t>
+          <t>126,32; 134,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,8; 135,94</t>
+          <t>128,66; 136,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133,18; 143,9</t>
+          <t>133,33; 143,95</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>126,11; 135,92</t>
+          <t>126,38; 135,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>131,31; 143,07</t>
+          <t>131,1; 143,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136,11; 153,46</t>
+          <t>136,08; 152,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123,47; 134,45</t>
+          <t>123,28; 133,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>133,09; 143,8</t>
+          <t>133,36; 143,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>127,16; 144,93</t>
+          <t>126,67; 144,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>125,77; 133,19</t>
+          <t>126,19; 133,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,13; 141,73</t>
+          <t>134,18; 142,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134,45; 146,47</t>
+          <t>134,62; 146,77</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>118,41; 133,63</t>
+          <t>118,26; 133,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123,0; 134,2</t>
+          <t>123,55; 134,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119,17; 136,15</t>
+          <t>118,91; 136,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124,9; 140,92</t>
+          <t>124,51; 142,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>129,11; 141,59</t>
+          <t>129,69; 142,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>132,84; 148,65</t>
+          <t>132,7; 149,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>123,59; 135,02</t>
+          <t>123,62; 135,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>128,0; 136,73</t>
+          <t>128,04; 136,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127,99; 140,74</t>
+          <t>128,79; 141,19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129,47; 140,35</t>
+          <t>129,58; 140,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131,27; 141,71</t>
+          <t>131,12; 142,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129,43; 144,66</t>
+          <t>128,5; 145,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,61; 143,57</t>
+          <t>130,48; 143,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130,84; 142,98</t>
+          <t>130,8; 143,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>130,06; 147,95</t>
+          <t>130,74; 147,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131,99; 140,38</t>
+          <t>131,85; 139,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>132,29; 140,42</t>
+          <t>132,61; 140,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132,11; 143,44</t>
+          <t>131,43; 143,7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,22; 135,58</t>
+          <t>127,56; 135,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>128,86; 135,08</t>
+          <t>128,78; 135,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124,49; 143,19</t>
+          <t>125,61; 144,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126,16; 134,67</t>
+          <t>126,27; 134,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>128,24; 135,38</t>
+          <t>127,91; 135,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>138,23; 148,29</t>
+          <t>138,5; 148,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>128,09; 133,75</t>
+          <t>127,82; 133,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>129,66; 134,66</t>
+          <t>129,55; 134,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135,65; 144,79</t>
+          <t>135,72; 144,91</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>124,23; 130,61</t>
+          <t>124,57; 130,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>126,65; 133,11</t>
+          <t>126,43; 133,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132,87; 142,22</t>
+          <t>132,8; 141,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124,92; 131,24</t>
+          <t>124,71; 131,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>126,06; 132,59</t>
+          <t>125,72; 132,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>138,41; 147,52</t>
+          <t>138,92; 147,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>125,5; 130,07</t>
+          <t>125,45; 130,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>127,16; 131,73</t>
+          <t>127,27; 131,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>137,44; 144,43</t>
+          <t>137,52; 144,69</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>127,5; 130,83</t>
+          <t>127,54; 130,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130,51; 133,66</t>
+          <t>130,44; 133,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134,98; 145,4</t>
+          <t>135,0; 144,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128,32; 131,92</t>
+          <t>128,44; 131,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>130,54; 133,79</t>
+          <t>130,52; 133,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>137,77; 142,73</t>
+          <t>137,86; 143,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>128,44; 130,85</t>
+          <t>128,6; 130,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>130,92; 133,24</t>
+          <t>130,94; 133,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>137,38; 142,78</t>
+          <t>137,28; 142,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
+          <t>Talla media, en centímetros, recogida por medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>123,51; 135,43</t>
+          <t>123,56; 136,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122,85; 134,29</t>
+          <t>123,1; 134,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121,52; 136,85</t>
+          <t>120,78; 136,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123,05; 134,16</t>
+          <t>122,83; 134,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>126,44; 138,88</t>
+          <t>126,08; 138,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>125,53; 142,15</t>
+          <t>125,57; 141,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>125,0; 133,25</t>
+          <t>124,47; 133,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>126,55; 135,07</t>
+          <t>126,73; 135,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>125,9; 136,93</t>
+          <t>126,31; 136,97</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>122,8; 132,3</t>
+          <t>123,24; 132,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127,44; 136,58</t>
+          <t>127,46; 135,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,89; 157,45</t>
+          <t>131,9; 157,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124,04; 132,48</t>
+          <t>124,03; 132,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>125,66; 134,23</t>
+          <t>126,13; 134,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>130,51; 149,71</t>
+          <t>130,95; 149,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>125,13; 131,39</t>
+          <t>124,99; 131,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>128,25; 133,96</t>
+          <t>128,05; 134,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>134,77; 153,59</t>
+          <t>135,07; 153,17</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>121,03; 131,02</t>
+          <t>121,25; 131,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127,57; 138,17</t>
+          <t>128,03; 138,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133,52; 147,03</t>
+          <t>133,69; 147,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128,94; 140,9</t>
+          <t>128,67; 140,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126,28; 136,34</t>
+          <t>125,79; 136,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>129,1; 144,61</t>
+          <t>128,99; 144,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126,32; 134,41</t>
+          <t>126,31; 134,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,66; 136,16</t>
+          <t>128,24; 136,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133,33; 143,95</t>
+          <t>133,42; 144,47</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>126,38; 135,99</t>
+          <t>126,0; 135,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>131,1; 143,08</t>
+          <t>131,69; 143,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136,08; 152,68</t>
+          <t>136,04; 152,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123,28; 133,38</t>
+          <t>123,24; 133,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>133,36; 143,63</t>
+          <t>133,02; 143,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>126,67; 144,19</t>
+          <t>125,88; 143,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,19; 133,18</t>
+          <t>126,12; 133,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,18; 142,26</t>
+          <t>134,02; 142,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134,62; 146,77</t>
+          <t>134,02; 146,74</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>118,26; 133,13</t>
+          <t>117,37; 133,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123,55; 134,67</t>
+          <t>123,13; 134,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118,91; 136,55</t>
+          <t>118,65; 136,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124,51; 142,16</t>
+          <t>123,2; 140,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>129,69; 142,27</t>
+          <t>129,73; 141,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>132,7; 149,0</t>
+          <t>133,31; 149,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>123,62; 135,36</t>
+          <t>122,98; 135,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>128,04; 136,85</t>
+          <t>127,77; 136,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>128,79; 141,19</t>
+          <t>128,8; 141,12</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129,58; 140,02</t>
+          <t>129,3; 139,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131,12; 142,35</t>
+          <t>131,07; 142,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128,5; 145,13</t>
+          <t>128,05; 144,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,48; 143,04</t>
+          <t>130,48; 143,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130,8; 143,49</t>
+          <t>130,08; 141,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>130,74; 147,2</t>
+          <t>129,82; 145,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131,85; 139,9</t>
+          <t>131,71; 140,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>132,61; 140,27</t>
+          <t>132,13; 140,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131,43; 143,7</t>
+          <t>132,08; 144,37</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,56; 135,23</t>
+          <t>127,24; 135,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>128,78; 135,41</t>
+          <t>128,69; 135,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125,61; 144,09</t>
+          <t>126,01; 143,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126,27; 134,74</t>
+          <t>126,38; 134,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>127,91; 135,66</t>
+          <t>127,92; 136,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>138,5; 148,02</t>
+          <t>138,6; 148,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>127,82; 133,67</t>
+          <t>128,2; 133,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>129,55; 134,37</t>
+          <t>129,48; 134,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135,72; 144,91</t>
+          <t>135,2; 145,04</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>124,57; 130,85</t>
+          <t>124,09; 130,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>126,43; 133,06</t>
+          <t>126,73; 133,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132,8; 141,53</t>
+          <t>132,99; 141,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124,71; 131,48</t>
+          <t>124,69; 131,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>125,72; 132,62</t>
+          <t>125,87; 132,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>138,92; 147,8</t>
+          <t>138,06; 147,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>125,45; 130,35</t>
+          <t>125,71; 130,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>127,27; 131,77</t>
+          <t>127,19; 131,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>137,52; 144,69</t>
+          <t>137,77; 144,59</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>127,54; 130,88</t>
+          <t>127,44; 130,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130,44; 133,69</t>
+          <t>130,37; 133,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135,0; 144,97</t>
+          <t>135,33; 146,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128,44; 131,98</t>
+          <t>128,56; 131,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>130,52; 133,84</t>
+          <t>130,42; 133,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>137,86; 143,05</t>
+          <t>137,61; 142,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>128,6; 130,91</t>
+          <t>128,65; 130,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>130,94; 133,26</t>
+          <t>130,96; 133,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>137,28; 142,7</t>
+          <t>137,22; 142,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>128,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>132,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>135,29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>129,53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>128,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>128,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>128,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>132,18</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>133,3</t>
+          <t>128,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>131,4</t>
+          <t>132,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>123,56; 136,39</t>
+          <t>122,68; 134,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123,1; 134,56</t>
+          <t>126,08; 138,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120,78; 136,35</t>
+          <t>127,54; 143,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122,83; 134,68</t>
+          <t>123,81; 135,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>126,08; 138,99</t>
+          <t>123,08; 134,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>125,57; 141,9</t>
+          <t>121,15; 137,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>124,47; 133,13</t>
+          <t>124,47; 133,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>126,73; 135,26</t>
+          <t>126,43; 135,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126,31; 136,97</t>
+          <t>127,09; 138,16</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128,24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>130,26</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>140,05</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>127,92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>132,06</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>146,82</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>128,24</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>130,26</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139,18</t>
+          <t>136,67</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>143,57</t>
+          <t>138,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>123,24; 132,67</t>
+          <t>124,16; 132,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127,46; 135,92</t>
+          <t>125,74; 134,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131,9; 157,01</t>
+          <t>132,48; 149,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124,03; 132,09</t>
+          <t>123,79; 133,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,13; 134,28</t>
+          <t>127,41; 136,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>130,95; 149,57</t>
+          <t>130,04; 144,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>124,99; 131,18</t>
+          <t>125,09; 131,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>128,05; 134,12</t>
+          <t>127,82; 134,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135,07; 153,17</t>
+          <t>132,82; 144,77</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>134,87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>131,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>137,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>126,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>133,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>141,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>134,87</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>131,22</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>136,87</t>
+          <t>141,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>138,75</t>
+          <t>139,39</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>121,25; 131,53</t>
+          <t>129,27; 140,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128,03; 138,39</t>
+          <t>125,67; 136,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133,69; 147,07</t>
+          <t>130,21; 146,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128,67; 140,47</t>
+          <t>121,0; 131,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125,79; 136,55</t>
+          <t>127,77; 138,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>128,99; 144,8</t>
+          <t>134,14; 147,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126,31; 134,41</t>
+          <t>126,8; 134,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,24; 136,01</t>
+          <t>128,8; 135,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133,42; 144,47</t>
+          <t>133,91; 144,4</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>127,96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>138,51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138,22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>131,29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>137,65</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>144,91</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>127,96</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>138,51</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>136,56</t>
+          <t>145,51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140,88</t>
+          <t>142,16</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>126,0; 135,76</t>
+          <t>123,47; 134,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>131,69; 143,64</t>
+          <t>133,09; 143,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136,04; 152,72</t>
+          <t>130,96; 145,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123,24; 133,18</t>
+          <t>126,11; 135,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>133,02; 143,84</t>
+          <t>131,31; 143,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>125,88; 143,82</t>
+          <t>136,53; 153,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,12; 133,05</t>
+          <t>125,77; 133,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,02; 142,17</t>
+          <t>134,13; 141,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134,02; 146,74</t>
+          <t>136,64; 147,74</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>132,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>135,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141,69</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>125,93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>128,7</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>128,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>132,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>135,71</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140,69</t>
+          <t>129,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135,05</t>
+          <t>135,9</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>117,37; 133,09</t>
+          <t>124,9; 140,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123,13; 134,36</t>
+          <t>129,11; 141,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118,65; 136,87</t>
+          <t>134,59; 149,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123,2; 140,64</t>
+          <t>118,41; 133,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>129,73; 141,85</t>
+          <t>123,0; 134,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133,31; 149,08</t>
+          <t>120,2; 136,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,98; 135,21</t>
+          <t>123,59; 135,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>127,77; 136,51</t>
+          <t>128,0; 136,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>128,8; 141,12</t>
+          <t>129,34; 141,42</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>136,83</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136,37</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>139,15</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>134,73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>136,86</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137,19</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>136,83</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>136,37</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>138,51</t>
+          <t>137,81</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138,0</t>
+          <t>138,59</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129,3; 139,92</t>
+          <t>130,61; 143,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131,07; 142,16</t>
+          <t>130,84; 142,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128,05; 144,23</t>
+          <t>130,58; 148,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,48; 143,29</t>
+          <t>129,47; 140,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130,08; 141,86</t>
+          <t>131,27; 141,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129,82; 145,88</t>
+          <t>130,26; 145,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131,71; 140,09</t>
+          <t>131,99; 140,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>132,13; 140,47</t>
+          <t>132,29; 140,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132,08; 144,37</t>
+          <t>132,72; 143,91</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130,4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>131,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>144,66</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>131,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>132,19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>137,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130,4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>131,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>143,53</t>
+          <t>140,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140,81</t>
+          <t>142,97</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,24; 135,28</t>
+          <t>126,16; 134,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>128,69; 135,35</t>
+          <t>128,24; 135,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126,01; 143,91</t>
+          <t>139,52; 149,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126,38; 134,6</t>
+          <t>127,22; 135,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>127,92; 136,0</t>
+          <t>128,86; 135,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>138,6; 148,51</t>
+          <t>133,62; 146,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>128,2; 133,95</t>
+          <t>128,09; 133,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>129,48; 134,49</t>
+          <t>129,66; 134,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135,2; 145,04</t>
+          <t>138,5; 146,5</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>128,25</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>129,16</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>144,45</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>127,58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>129,84</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>137,51</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>128,25</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>129,16</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>143,44</t>
+          <t>139,03</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>141,03</t>
+          <t>142,22</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>124,09; 130,53</t>
+          <t>124,92; 131,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>126,73; 133,12</t>
+          <t>126,06; 132,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132,99; 141,73</t>
+          <t>139,39; 148,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124,69; 131,42</t>
+          <t>124,23; 130,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>125,87; 132,45</t>
+          <t>126,65; 133,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>138,06; 147,52</t>
+          <t>134,47; 143,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>125,71; 130,28</t>
+          <t>125,5; 130,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>127,19; 131,61</t>
+          <t>127,16; 131,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>137,77; 144,59</t>
+          <t>138,74; 145,54</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>130,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>132,13</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>141,6</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>129,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>132,08</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>138,73</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>130,24</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>140,26</t>
+          <t>137,72</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>139,56</t>
+          <t>139,87</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>127,44; 130,91</t>
+          <t>128,32; 131,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130,37; 133,71</t>
+          <t>130,54; 133,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135,33; 146,78</t>
+          <t>139,17; 143,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128,56; 131,98</t>
+          <t>127,5; 130,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>130,42; 133,75</t>
+          <t>130,51; 133,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>137,61; 142,73</t>
+          <t>135,0; 140,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>128,65; 130,94</t>
+          <t>128,44; 130,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>130,96; 133,38</t>
+          <t>130,92; 133,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>137,22; 142,97</t>
+          <t>138,08; 141,53</t>
         </is>
       </c>
     </row>
